--- a/data/H131_20260620_12.xlsx
+++ b/data/H131_20260620_12.xlsx
@@ -598,7 +598,7 @@
         <v>1074.0</v>
       </c>
       <c r="J4" s="2">
-        <v>667.0</v>
+        <v>699.0</v>
       </c>
       <c r="K4" s="2">
         <v>1.0</v>
@@ -610,10 +610,10 @@
         <v>0.0</v>
       </c>
       <c r="N4" s="2">
-        <v>667.0</v>
+        <v>699.0</v>
       </c>
       <c r="O4" s="2">
-        <v>328.0</v>
+        <v>360.0</v>
       </c>
       <c r="P4" s="2">
         <v>339.0</v>
@@ -669,7 +669,7 @@
         <v>667.0</v>
       </c>
       <c r="J5" s="2">
-        <v>577.0</v>
+        <v>580.0</v>
       </c>
       <c r="K5" s="2">
         <v>1.0</v>
@@ -681,13 +681,13 @@
         <v>0.0</v>
       </c>
       <c r="N5" s="2">
-        <v>577.0</v>
+        <v>580.0</v>
       </c>
       <c r="O5" s="2">
-        <v>303.0</v>
+        <v>305.0</v>
       </c>
       <c r="P5" s="2">
-        <v>273.0</v>
+        <v>274.0</v>
       </c>
       <c r="Q5" s="2">
         <v>1.0</v>
@@ -740,7 +740,7 @@
         <v>929.0</v>
       </c>
       <c r="J6" s="2">
-        <v>804.0</v>
+        <v>814.0</v>
       </c>
       <c r="K6" s="2">
         <v>1.0</v>
@@ -752,13 +752,13 @@
         <v>0.0</v>
       </c>
       <c r="N6" s="2">
-        <v>804.0</v>
+        <v>814.0</v>
       </c>
       <c r="O6" s="2">
-        <v>430.0</v>
+        <v>436.0</v>
       </c>
       <c r="P6" s="2">
-        <v>374.0</v>
+        <v>378.0</v>
       </c>
       <c r="Q6" s="2">
         <v>0.0</v>
@@ -767,10 +767,10 @@
         <v>36.0</v>
       </c>
       <c r="S6" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="U6" s="2">
         <v>0.0</v>
@@ -779,7 +779,7 @@
         <v>0.0</v>
       </c>
       <c r="W6" s="2">
-        <v>36.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="7">
@@ -811,7 +811,7 @@
         <v>515.0</v>
       </c>
       <c r="J7" s="2">
-        <v>413.0</v>
+        <v>414.0</v>
       </c>
       <c r="K7" s="2">
         <v>1.0</v>
@@ -823,10 +823,10 @@
         <v>0.0</v>
       </c>
       <c r="N7" s="2">
-        <v>413.0</v>
+        <v>414.0</v>
       </c>
       <c r="O7" s="2">
-        <v>229.0</v>
+        <v>230.0</v>
       </c>
       <c r="P7" s="2">
         <v>184.0</v>
@@ -841,7 +841,7 @@
         <v>8.0</v>
       </c>
       <c r="T7" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U7" s="2">
         <v>0.0</v>
@@ -850,7 +850,7 @@
         <v>0.0</v>
       </c>
       <c r="W7" s="2">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="8">
@@ -882,7 +882,7 @@
         <v>711.0</v>
       </c>
       <c r="J8" s="2">
-        <v>576.0</v>
+        <v>577.0</v>
       </c>
       <c r="K8" s="2">
         <v>1.0</v>
@@ -894,10 +894,10 @@
         <v>0.0</v>
       </c>
       <c r="N8" s="2">
-        <v>576.0</v>
+        <v>577.0</v>
       </c>
       <c r="O8" s="2">
-        <v>335.0</v>
+        <v>336.0</v>
       </c>
       <c r="P8" s="2">
         <v>241.0</v>
@@ -977,7 +977,7 @@
         <v>0.0</v>
       </c>
       <c r="R9" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S9" s="2">
         <v>9.0</v>
@@ -992,7 +992,7 @@
         <v>0.0</v>
       </c>
       <c r="W9" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="10">
@@ -1024,7 +1024,7 @@
         <v>311.0</v>
       </c>
       <c r="J10" s="2">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="K10" s="2">
         <v>1.0</v>
@@ -1036,10 +1036,10 @@
         <v>0.0</v>
       </c>
       <c r="N10" s="2">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="O10" s="2">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="P10" s="2">
         <v>127.0</v>
@@ -1166,7 +1166,7 @@
         <v>815.0</v>
       </c>
       <c r="J12" s="2">
-        <v>760.0</v>
+        <v>761.0</v>
       </c>
       <c r="K12" s="2">
         <v>1.0</v>
@@ -1178,10 +1178,10 @@
         <v>0.0</v>
       </c>
       <c r="N12" s="2">
-        <v>760.0</v>
+        <v>761.0</v>
       </c>
       <c r="O12" s="2">
-        <v>436.0</v>
+        <v>437.0</v>
       </c>
       <c r="P12" s="2">
         <v>324.0</v>
@@ -1308,7 +1308,7 @@
         <v>1342.0</v>
       </c>
       <c r="J14" s="2">
-        <v>1148.0</v>
+        <v>1172.0</v>
       </c>
       <c r="K14" s="2">
         <v>1.0</v>
@@ -1320,19 +1320,19 @@
         <v>0.0</v>
       </c>
       <c r="N14" s="2">
-        <v>1148.0</v>
+        <v>1172.0</v>
       </c>
       <c r="O14" s="2">
-        <v>651.0</v>
+        <v>663.0</v>
       </c>
       <c r="P14" s="2">
-        <v>495.0</v>
+        <v>507.0</v>
       </c>
       <c r="Q14" s="2">
         <v>2.0</v>
       </c>
       <c r="R14" s="2">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="S14" s="2">
         <v>30.0</v>
@@ -1341,13 +1341,13 @@
         <v>4.0</v>
       </c>
       <c r="U14" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="V14" s="2">
         <v>0.0</v>
       </c>
       <c r="W14" s="2">
-        <v>69.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="15">
@@ -1379,7 +1379,7 @@
         <v>791.0</v>
       </c>
       <c r="J15" s="2">
-        <v>697.0</v>
+        <v>712.0</v>
       </c>
       <c r="K15" s="2">
         <v>1.0</v>
@@ -1391,16 +1391,16 @@
         <v>0.0</v>
       </c>
       <c r="N15" s="2">
-        <v>697.0</v>
+        <v>712.0</v>
       </c>
       <c r="O15" s="2">
-        <v>352.0</v>
+        <v>353.0</v>
       </c>
       <c r="P15" s="2">
-        <v>345.0</v>
+        <v>351.0</v>
       </c>
       <c r="Q15" s="2">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="R15" s="2">
         <v>21.0</v>
@@ -1412,13 +1412,13 @@
         <v>0.0</v>
       </c>
       <c r="U15" s="2">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="V15" s="2">
         <v>0.0</v>
       </c>
       <c r="W15" s="2">
-        <v>42.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="16">
@@ -1450,7 +1450,7 @@
         <v>692.0</v>
       </c>
       <c r="J16" s="2">
-        <v>576.0</v>
+        <v>577.0</v>
       </c>
       <c r="K16" s="2">
         <v>1.0</v>
@@ -1462,10 +1462,10 @@
         <v>0.0</v>
       </c>
       <c r="N16" s="2">
-        <v>576.0</v>
+        <v>577.0</v>
       </c>
       <c r="O16" s="2">
-        <v>281.0</v>
+        <v>282.0</v>
       </c>
       <c r="P16" s="2">
         <v>295.0</v>
@@ -1483,13 +1483,13 @@
         <v>11.0</v>
       </c>
       <c r="U16" s="2">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
       <c r="V16" s="2">
         <v>0.0</v>
       </c>
       <c r="W16" s="2">
-        <v>98.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="17">
@@ -1592,7 +1592,7 @@
         <v>1182.0</v>
       </c>
       <c r="J18" s="2">
-        <v>1127.0</v>
+        <v>1128.0</v>
       </c>
       <c r="K18" s="2">
         <v>1.0</v>
@@ -1604,10 +1604,10 @@
         <v>0.0</v>
       </c>
       <c r="N18" s="2">
-        <v>1127.0</v>
+        <v>1128.0</v>
       </c>
       <c r="O18" s="2">
-        <v>599.0</v>
+        <v>600.0</v>
       </c>
       <c r="P18" s="2">
         <v>528.0</v>
@@ -1663,7 +1663,7 @@
         <v>940.0</v>
       </c>
       <c r="J19" s="2">
-        <v>811.0</v>
+        <v>816.0</v>
       </c>
       <c r="K19" s="2">
         <v>1.0</v>
@@ -1675,13 +1675,13 @@
         <v>0.0</v>
       </c>
       <c r="N19" s="2">
-        <v>811.0</v>
+        <v>816.0</v>
       </c>
       <c r="O19" s="2">
-        <v>428.0</v>
+        <v>431.0</v>
       </c>
       <c r="P19" s="2">
-        <v>383.0</v>
+        <v>385.0</v>
       </c>
       <c r="Q19" s="2">
         <v>0.0</v>
@@ -1838,13 +1838,13 @@
         <v>4.0</v>
       </c>
       <c r="U21" s="2">
-        <v>26.0</v>
+        <v>51.0</v>
       </c>
       <c r="V21" s="2">
         <v>0.0</v>
       </c>
       <c r="W21" s="2">
-        <v>98.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -1947,7 +1947,7 @@
         <v>762.0</v>
       </c>
       <c r="J23" s="2">
-        <v>445.0</v>
+        <v>470.0</v>
       </c>
       <c r="K23" s="2">
         <v>1.0</v>
@@ -1959,13 +1959,13 @@
         <v>0.0</v>
       </c>
       <c r="N23" s="2">
-        <v>445.0</v>
+        <v>470.0</v>
       </c>
       <c r="O23" s="2">
-        <v>220.0</v>
+        <v>238.0</v>
       </c>
       <c r="P23" s="2">
-        <v>225.0</v>
+        <v>232.0</v>
       </c>
       <c r="Q23" s="2">
         <v>0.0</v>
@@ -2018,7 +2018,7 @@
         <v>1296.0</v>
       </c>
       <c r="J24" s="2">
-        <v>864.0</v>
+        <v>923.0</v>
       </c>
       <c r="K24" s="2">
         <v>1.0</v>
@@ -2030,13 +2030,13 @@
         <v>0.0</v>
       </c>
       <c r="N24" s="2">
-        <v>864.0</v>
+        <v>923.0</v>
       </c>
       <c r="O24" s="2">
-        <v>507.0</v>
+        <v>540.0</v>
       </c>
       <c r="P24" s="2">
-        <v>341.0</v>
+        <v>367.0</v>
       </c>
       <c r="Q24" s="2">
         <v>16.0</v>
@@ -2160,7 +2160,7 @@
         <v>1399.0</v>
       </c>
       <c r="J26" s="2">
-        <v>1196.0</v>
+        <v>1217.0</v>
       </c>
       <c r="K26" s="2">
         <v>1.0</v>
@@ -2172,13 +2172,13 @@
         <v>0.0</v>
       </c>
       <c r="N26" s="2">
-        <v>1196.0</v>
+        <v>1217.0</v>
       </c>
       <c r="O26" s="2">
-        <v>645.0</v>
+        <v>662.0</v>
       </c>
       <c r="P26" s="2">
-        <v>551.0</v>
+        <v>555.0</v>
       </c>
       <c r="Q26" s="2">
         <v>0.0</v>
@@ -2373,7 +2373,7 @@
         <v>1280.0</v>
       </c>
       <c r="J29" s="2">
-        <v>752.0</v>
+        <v>761.0</v>
       </c>
       <c r="K29" s="2">
         <v>1.0</v>
@@ -2385,13 +2385,13 @@
         <v>0.0</v>
       </c>
       <c r="N29" s="2">
-        <v>752.0</v>
+        <v>761.0</v>
       </c>
       <c r="O29" s="2">
-        <v>221.0</v>
+        <v>227.0</v>
       </c>
       <c r="P29" s="2">
-        <v>399.0</v>
+        <v>402.0</v>
       </c>
       <c r="Q29" s="2">
         <v>132.0</v>
@@ -2444,7 +2444,7 @@
         <v>258.0</v>
       </c>
       <c r="J30" s="2">
-        <v>236.0</v>
+        <v>239.0</v>
       </c>
       <c r="K30" s="2">
         <v>1.0</v>
@@ -2456,13 +2456,13 @@
         <v>0.0</v>
       </c>
       <c r="N30" s="2">
-        <v>236.0</v>
+        <v>239.0</v>
       </c>
       <c r="O30" s="2">
-        <v>133.0</v>
+        <v>135.0</v>
       </c>
       <c r="P30" s="2">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="Q30" s="2">
         <v>22.0</v>
@@ -2515,7 +2515,7 @@
         <v>1214.0</v>
       </c>
       <c r="J31" s="2">
-        <v>1024.0</v>
+        <v>1044.0</v>
       </c>
       <c r="K31" s="2">
         <v>1.0</v>
@@ -2527,19 +2527,19 @@
         <v>0.0</v>
       </c>
       <c r="N31" s="2">
-        <v>1024.0</v>
+        <v>1044.0</v>
       </c>
       <c r="O31" s="2">
-        <v>562.0</v>
+        <v>571.0</v>
       </c>
       <c r="P31" s="2">
-        <v>451.0</v>
+        <v>461.0</v>
       </c>
       <c r="Q31" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R31" s="2">
-        <v>29.0</v>
+        <v>54.0</v>
       </c>
       <c r="S31" s="2">
         <v>14.0</v>
@@ -2548,13 +2548,13 @@
         <v>0.0</v>
       </c>
       <c r="U31" s="2">
-        <v>23.0</v>
+        <v>31.0</v>
       </c>
       <c r="V31" s="2">
         <v>8.0</v>
       </c>
       <c r="W31" s="2">
-        <v>74.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -2657,7 +2657,7 @@
         <v>346.0</v>
       </c>
       <c r="J33" s="2">
-        <v>317.0</v>
+        <v>318.0</v>
       </c>
       <c r="K33" s="2">
         <v>1.0</v>
@@ -2669,10 +2669,10 @@
         <v>0.0</v>
       </c>
       <c r="N33" s="2">
-        <v>317.0</v>
+        <v>318.0</v>
       </c>
       <c r="O33" s="2">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="P33" s="2">
         <v>174.0</v>
@@ -2799,7 +2799,7 @@
         <v>554.0</v>
       </c>
       <c r="J35" s="2">
-        <v>509.0</v>
+        <v>522.0</v>
       </c>
       <c r="K35" s="2">
         <v>1.0</v>
@@ -2811,16 +2811,16 @@
         <v>0.0</v>
       </c>
       <c r="N35" s="2">
-        <v>509.0</v>
+        <v>522.0</v>
       </c>
       <c r="O35" s="2">
-        <v>277.0</v>
+        <v>284.0</v>
       </c>
       <c r="P35" s="2">
-        <v>220.0</v>
+        <v>222.0</v>
       </c>
       <c r="Q35" s="2">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="R35" s="2">
         <v>16.0</v>
@@ -2870,7 +2870,7 @@
         <v>1103.0</v>
       </c>
       <c r="J36" s="2">
-        <v>729.0</v>
+        <v>736.0</v>
       </c>
       <c r="K36" s="2">
         <v>1.0</v>
@@ -2882,13 +2882,13 @@
         <v>0.0</v>
       </c>
       <c r="N36" s="2">
-        <v>729.0</v>
+        <v>736.0</v>
       </c>
       <c r="O36" s="2">
-        <v>350.0</v>
+        <v>353.0</v>
       </c>
       <c r="P36" s="2">
-        <v>372.0</v>
+        <v>376.0</v>
       </c>
       <c r="Q36" s="2">
         <v>7.0</v>
@@ -3012,7 +3012,7 @@
         <v>1123.0</v>
       </c>
       <c r="J38" s="2">
-        <v>978.0</v>
+        <v>986.0</v>
       </c>
       <c r="K38" s="2">
         <v>1.0</v>
@@ -3024,19 +3024,19 @@
         <v>0.0</v>
       </c>
       <c r="N38" s="2">
-        <v>978.0</v>
+        <v>986.0</v>
       </c>
       <c r="O38" s="2">
-        <v>575.0</v>
+        <v>578.0</v>
       </c>
       <c r="P38" s="2">
-        <v>403.0</v>
+        <v>408.0</v>
       </c>
       <c r="Q38" s="2">
         <v>0.0</v>
       </c>
       <c r="R38" s="2">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="S38" s="2">
         <v>4.0</v>
@@ -3051,7 +3051,7 @@
         <v>0.0</v>
       </c>
       <c r="W38" s="2">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -3083,7 +3083,7 @@
         <v>588.0</v>
       </c>
       <c r="J39" s="2">
-        <v>527.0</v>
+        <v>532.0</v>
       </c>
       <c r="K39" s="2">
         <v>1.0</v>
@@ -3095,13 +3095,13 @@
         <v>0.0</v>
       </c>
       <c r="N39" s="2">
-        <v>527.0</v>
+        <v>532.0</v>
       </c>
       <c r="O39" s="2">
-        <v>276.0</v>
+        <v>278.0</v>
       </c>
       <c r="P39" s="2">
-        <v>251.0</v>
+        <v>254.0</v>
       </c>
       <c r="Q39" s="2">
         <v>0.0</v>
@@ -3225,7 +3225,7 @@
         <v>1244.0</v>
       </c>
       <c r="J41" s="2">
-        <v>1056.0</v>
+        <v>1059.0</v>
       </c>
       <c r="K41" s="2">
         <v>1.0</v>
@@ -3237,10 +3237,10 @@
         <v>0.0</v>
       </c>
       <c r="N41" s="2">
-        <v>1056.0</v>
+        <v>1059.0</v>
       </c>
       <c r="O41" s="2">
-        <v>540.0</v>
+        <v>543.0</v>
       </c>
       <c r="P41" s="2">
         <v>516.0</v>
@@ -3249,10 +3249,10 @@
         <v>0.0</v>
       </c>
       <c r="R41" s="2">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="S41" s="2">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="T41" s="2">
         <v>0.0</v>
@@ -3264,7 +3264,7 @@
         <v>0.0</v>
       </c>
       <c r="W41" s="2">
-        <v>11.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
@@ -3296,7 +3296,7 @@
         <v>1005.0</v>
       </c>
       <c r="J42" s="2">
-        <v>724.0</v>
+        <v>759.0</v>
       </c>
       <c r="K42" s="2">
         <v>1.0</v>
@@ -3308,19 +3308,19 @@
         <v>0.0</v>
       </c>
       <c r="N42" s="2">
-        <v>724.0</v>
+        <v>759.0</v>
       </c>
       <c r="O42" s="2">
-        <v>470.0</v>
+        <v>503.0</v>
       </c>
       <c r="P42" s="2">
-        <v>254.0</v>
+        <v>255.0</v>
       </c>
       <c r="Q42" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R42" s="2">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="S42" s="2">
         <v>3.0</v>
@@ -3335,7 +3335,7 @@
         <v>0.0</v>
       </c>
       <c r="W42" s="2">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -3509,7 +3509,7 @@
         <v>1213.0</v>
       </c>
       <c r="J45" s="2">
-        <v>1088.0</v>
+        <v>1095.0</v>
       </c>
       <c r="K45" s="2">
         <v>1.0</v>
@@ -3521,22 +3521,22 @@
         <v>1.0</v>
       </c>
       <c r="N45" s="2">
-        <v>1087.0</v>
+        <v>1094.0</v>
       </c>
       <c r="O45" s="2">
-        <v>512.0</v>
+        <v>514.0</v>
       </c>
       <c r="P45" s="2">
-        <v>539.0</v>
+        <v>542.0</v>
       </c>
       <c r="Q45" s="2">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="R45" s="2">
         <v>52.0</v>
       </c>
       <c r="S45" s="2">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="T45" s="2">
         <v>3.0</v>
@@ -3548,7 +3548,7 @@
         <v>0.0</v>
       </c>
       <c r="W45" s="2">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
@@ -3651,7 +3651,7 @@
         <v>796.0</v>
       </c>
       <c r="J47" s="2">
-        <v>733.0</v>
+        <v>734.0</v>
       </c>
       <c r="K47" s="2">
         <v>1.0</v>
@@ -3663,10 +3663,10 @@
         <v>0.0</v>
       </c>
       <c r="N47" s="2">
-        <v>733.0</v>
+        <v>734.0</v>
       </c>
       <c r="O47" s="2">
-        <v>399.0</v>
+        <v>400.0</v>
       </c>
       <c r="P47" s="2">
         <v>333.0</v>
@@ -3722,7 +3722,7 @@
         <v>1102.0</v>
       </c>
       <c r="J48" s="2">
-        <v>954.0</v>
+        <v>968.0</v>
       </c>
       <c r="K48" s="2">
         <v>1.0</v>
@@ -3734,13 +3734,13 @@
         <v>0.0</v>
       </c>
       <c r="N48" s="2">
-        <v>954.0</v>
+        <v>968.0</v>
       </c>
       <c r="O48" s="2">
-        <v>557.0</v>
+        <v>570.0</v>
       </c>
       <c r="P48" s="2">
-        <v>397.0</v>
+        <v>398.0</v>
       </c>
       <c r="Q48" s="2">
         <v>0.0</v>
@@ -3749,7 +3749,7 @@
         <v>30.0</v>
       </c>
       <c r="S48" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="T48" s="2">
         <v>0.0</v>
@@ -3761,7 +3761,7 @@
         <v>0.0</v>
       </c>
       <c r="W48" s="2">
-        <v>40.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
@@ -3793,7 +3793,7 @@
         <v>1437.0</v>
       </c>
       <c r="J49" s="2">
-        <v>1189.0</v>
+        <v>1196.0</v>
       </c>
       <c r="K49" s="2">
         <v>1.0</v>
@@ -3805,19 +3805,19 @@
         <v>0.0</v>
       </c>
       <c r="N49" s="2">
-        <v>1189.0</v>
+        <v>1196.0</v>
       </c>
       <c r="O49" s="2">
-        <v>666.0</v>
+        <v>670.0</v>
       </c>
       <c r="P49" s="2">
-        <v>489.0</v>
+        <v>491.0</v>
       </c>
       <c r="Q49" s="2">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="R49" s="2">
-        <v>50.0</v>
+        <v>56.0</v>
       </c>
       <c r="S49" s="2">
         <v>8.0</v>
@@ -3832,7 +3832,7 @@
         <v>0.0</v>
       </c>
       <c r="W49" s="2">
-        <v>58.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
@@ -4219,7 +4219,7 @@
         <v>540.0</v>
       </c>
       <c r="J55" s="2">
-        <v>456.0</v>
+        <v>487.0</v>
       </c>
       <c r="K55" s="2">
         <v>1.0</v>
@@ -4231,22 +4231,22 @@
         <v>0.0</v>
       </c>
       <c r="N55" s="2">
-        <v>456.0</v>
+        <v>487.0</v>
       </c>
       <c r="O55" s="2">
-        <v>217.0</v>
+        <v>227.0</v>
       </c>
       <c r="P55" s="2">
-        <v>239.0</v>
+        <v>243.0</v>
       </c>
       <c r="Q55" s="2">
-        <v>0.0</v>
+        <v>17.0</v>
       </c>
       <c r="R55" s="2">
         <v>19.0</v>
       </c>
       <c r="S55" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="T55" s="2">
         <v>0.0</v>
@@ -4258,7 +4258,7 @@
         <v>0.0</v>
       </c>
       <c r="W55" s="2">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
@@ -4290,7 +4290,7 @@
         <v>615.0</v>
       </c>
       <c r="J56" s="2">
-        <v>586.0</v>
+        <v>587.0</v>
       </c>
       <c r="K56" s="2">
         <v>1.0</v>
@@ -4302,10 +4302,10 @@
         <v>0.0</v>
       </c>
       <c r="N56" s="2">
-        <v>586.0</v>
+        <v>587.0</v>
       </c>
       <c r="O56" s="2">
-        <v>295.0</v>
+        <v>296.0</v>
       </c>
       <c r="P56" s="2">
         <v>291.0</v>
@@ -4858,7 +4858,7 @@
         <v>1113.0</v>
       </c>
       <c r="J64" s="2">
-        <v>1077.0</v>
+        <v>1078.0</v>
       </c>
       <c r="K64" s="2">
         <v>1.0</v>
@@ -4870,10 +4870,10 @@
         <v>0.0</v>
       </c>
       <c r="N64" s="2">
-        <v>1077.0</v>
+        <v>1078.0</v>
       </c>
       <c r="O64" s="2">
-        <v>616.0</v>
+        <v>617.0</v>
       </c>
       <c r="P64" s="2">
         <v>461.0</v>
@@ -5805,7 +5805,7 @@
         <v>157.0</v>
       </c>
       <c r="R77" s="2">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
       <c r="S77" s="2">
         <v>0.0</v>
@@ -5820,7 +5820,7 @@
         <v>0.0</v>
       </c>
       <c r="W77" s="2">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
@@ -5852,7 +5852,7 @@
         <v>1275.0</v>
       </c>
       <c r="J78" s="2">
-        <v>762.0</v>
+        <v>766.0</v>
       </c>
       <c r="K78" s="2">
         <v>1.0</v>
@@ -5864,13 +5864,13 @@
         <v>0.0</v>
       </c>
       <c r="N78" s="2">
-        <v>762.0</v>
+        <v>766.0</v>
       </c>
       <c r="O78" s="2">
-        <v>305.0</v>
+        <v>307.0</v>
       </c>
       <c r="P78" s="2">
-        <v>457.0</v>
+        <v>459.0</v>
       </c>
       <c r="Q78" s="2">
         <v>0.0</v>
@@ -5923,7 +5923,7 @@
         <v>787.0</v>
       </c>
       <c r="J79" s="2">
-        <v>616.0</v>
+        <v>620.0</v>
       </c>
       <c r="K79" s="2">
         <v>1.0</v>
@@ -5935,19 +5935,19 @@
         <v>0.0</v>
       </c>
       <c r="N79" s="2">
-        <v>616.0</v>
+        <v>620.0</v>
       </c>
       <c r="O79" s="2">
-        <v>366.0</v>
+        <v>369.0</v>
       </c>
       <c r="P79" s="2">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="Q79" s="2">
         <v>0.0</v>
       </c>
       <c r="R79" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="S79" s="2">
         <v>9.0</v>
@@ -5962,7 +5962,7 @@
         <v>0.0</v>
       </c>
       <c r="W79" s="2">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
@@ -6018,11 +6018,11 @@
         <v>7.0</v>
       </c>
       <c r="R80" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="S80" s="2">
         <v>2.0</v>
       </c>
-      <c r="S80" s="2">
-        <v>0.0</v>
-      </c>
       <c r="T80" s="2">
         <v>0.0</v>
       </c>
@@ -6033,7 +6033,7 @@
         <v>0.0</v>
       </c>
       <c r="W80" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
@@ -6065,7 +6065,7 @@
         <v>796.0</v>
       </c>
       <c r="J81" s="2">
-        <v>727.0</v>
+        <v>728.0</v>
       </c>
       <c r="K81" s="2">
         <v>1.0</v>
@@ -6077,7 +6077,7 @@
         <v>0.0</v>
       </c>
       <c r="N81" s="2">
-        <v>727.0</v>
+        <v>728.0</v>
       </c>
       <c r="O81" s="2">
         <v>379.0</v>
@@ -6086,7 +6086,7 @@
         <v>347.0</v>
       </c>
       <c r="Q81" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="R81" s="2">
         <v>18.0</v>
@@ -6098,13 +6098,13 @@
         <v>4.0</v>
       </c>
       <c r="U81" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V81" s="2">
         <v>0.0</v>
       </c>
       <c r="W81" s="2">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
@@ -6349,7 +6349,7 @@
         <v>1308.0</v>
       </c>
       <c r="J85" s="2">
-        <v>1211.0</v>
+        <v>1213.0</v>
       </c>
       <c r="K85" s="2">
         <v>1.0</v>
@@ -6361,16 +6361,16 @@
         <v>0.0</v>
       </c>
       <c r="N85" s="2">
-        <v>1211.0</v>
+        <v>1213.0</v>
       </c>
       <c r="O85" s="2">
-        <v>594.0</v>
+        <v>595.0</v>
       </c>
       <c r="P85" s="2">
         <v>606.0</v>
       </c>
       <c r="Q85" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R85" s="2">
         <v>43.0</v>
@@ -6420,7 +6420,7 @@
         <v>1249.0</v>
       </c>
       <c r="J86" s="2">
-        <v>1154.0</v>
+        <v>1162.0</v>
       </c>
       <c r="K86" s="2">
         <v>1.0</v>
@@ -6432,13 +6432,13 @@
         <v>0.0</v>
       </c>
       <c r="N86" s="2">
-        <v>1154.0</v>
+        <v>1162.0</v>
       </c>
       <c r="O86" s="2">
-        <v>631.0</v>
+        <v>638.0</v>
       </c>
       <c r="P86" s="2">
-        <v>523.0</v>
+        <v>524.0</v>
       </c>
       <c r="Q86" s="2">
         <v>0.0</v>
@@ -6562,7 +6562,7 @@
         <v>883.0</v>
       </c>
       <c r="J88" s="2">
-        <v>723.0</v>
+        <v>732.0</v>
       </c>
       <c r="K88" s="2">
         <v>1.0</v>
@@ -6574,19 +6574,19 @@
         <v>0.0</v>
       </c>
       <c r="N88" s="2">
-        <v>723.0</v>
+        <v>732.0</v>
       </c>
       <c r="O88" s="2">
-        <v>369.0</v>
+        <v>375.0</v>
       </c>
       <c r="P88" s="2">
-        <v>354.0</v>
+        <v>357.0</v>
       </c>
       <c r="Q88" s="2">
         <v>0.0</v>
       </c>
       <c r="R88" s="2">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="S88" s="2">
         <v>26.0</v>
@@ -6601,7 +6601,7 @@
         <v>1.0</v>
       </c>
       <c r="W88" s="2">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
@@ -6633,7 +6633,7 @@
         <v>814.0</v>
       </c>
       <c r="J89" s="2">
-        <v>700.0</v>
+        <v>714.0</v>
       </c>
       <c r="K89" s="2">
         <v>1.0</v>
@@ -6645,13 +6645,13 @@
         <v>0.0</v>
       </c>
       <c r="N89" s="2">
-        <v>700.0</v>
+        <v>714.0</v>
       </c>
       <c r="O89" s="2">
-        <v>394.0</v>
+        <v>400.0</v>
       </c>
       <c r="P89" s="2">
-        <v>306.0</v>
+        <v>314.0</v>
       </c>
       <c r="Q89" s="2">
         <v>0.0</v>
@@ -6666,13 +6666,13 @@
         <v>0.0</v>
       </c>
       <c r="U89" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="V89" s="2">
         <v>0.0</v>
       </c>
       <c r="W89" s="2">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
@@ -6790,13 +6790,13 @@
         <v>727.0</v>
       </c>
       <c r="O91" s="2">
-        <v>180.0</v>
+        <v>187.0</v>
       </c>
       <c r="P91" s="2">
-        <v>338.0</v>
+        <v>339.0</v>
       </c>
       <c r="Q91" s="2">
-        <v>209.0</v>
+        <v>201.0</v>
       </c>
       <c r="R91" s="2">
         <v>44.0</v>
@@ -6846,7 +6846,7 @@
         <v>1315.0</v>
       </c>
       <c r="J92" s="2">
-        <v>802.0</v>
+        <v>809.0</v>
       </c>
       <c r="K92" s="2">
         <v>1.0</v>
@@ -6858,13 +6858,13 @@
         <v>0.0</v>
       </c>
       <c r="N92" s="2">
-        <v>802.0</v>
+        <v>809.0</v>
       </c>
       <c r="O92" s="2">
-        <v>382.0</v>
+        <v>386.0</v>
       </c>
       <c r="P92" s="2">
-        <v>320.0</v>
+        <v>323.0</v>
       </c>
       <c r="Q92" s="2">
         <v>100.0</v>
@@ -6917,7 +6917,7 @@
         <v>960.0</v>
       </c>
       <c r="J93" s="2">
-        <v>849.0</v>
+        <v>853.0</v>
       </c>
       <c r="K93" s="2">
         <v>1.0</v>
@@ -6929,10 +6929,10 @@
         <v>0.0</v>
       </c>
       <c r="N93" s="2">
-        <v>849.0</v>
+        <v>853.0</v>
       </c>
       <c r="O93" s="2">
-        <v>486.0</v>
+        <v>490.0</v>
       </c>
       <c r="P93" s="2">
         <v>362.0</v>
@@ -6947,7 +6947,7 @@
         <v>20.0</v>
       </c>
       <c r="T93" s="2">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="U93" s="2">
         <v>0.0</v>
@@ -6956,7 +6956,7 @@
         <v>2.0</v>
       </c>
       <c r="W93" s="2">
-        <v>91.0</v>
+        <v>93.0</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
@@ -7130,7 +7130,7 @@
         <v>1426.0</v>
       </c>
       <c r="J96" s="2">
-        <v>1084.0</v>
+        <v>1118.0</v>
       </c>
       <c r="K96" s="2">
         <v>1.0</v>
@@ -7142,13 +7142,13 @@
         <v>0.0</v>
       </c>
       <c r="N96" s="2">
-        <v>1084.0</v>
+        <v>1118.0</v>
       </c>
       <c r="O96" s="2">
-        <v>603.0</v>
+        <v>627.0</v>
       </c>
       <c r="P96" s="2">
-        <v>475.0</v>
+        <v>485.0</v>
       </c>
       <c r="Q96" s="2">
         <v>6.0</v>
@@ -7201,7 +7201,7 @@
         <v>1012.0</v>
       </c>
       <c r="J97" s="2">
-        <v>946.0</v>
+        <v>947.0</v>
       </c>
       <c r="K97" s="2">
         <v>1.0</v>
@@ -7213,10 +7213,10 @@
         <v>0.0</v>
       </c>
       <c r="N97" s="2">
-        <v>946.0</v>
+        <v>947.0</v>
       </c>
       <c r="O97" s="2">
-        <v>476.0</v>
+        <v>477.0</v>
       </c>
       <c r="P97" s="2">
         <v>452.0</v>
@@ -7272,7 +7272,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" s="2">
-        <v>1026.0</v>
+        <v>1033.0</v>
       </c>
       <c r="K98" s="2">
         <v>1.0</v>
@@ -7284,13 +7284,13 @@
         <v>0.0</v>
       </c>
       <c r="N98" s="2">
-        <v>1026.0</v>
+        <v>1033.0</v>
       </c>
       <c r="O98" s="2">
-        <v>530.0</v>
+        <v>534.0</v>
       </c>
       <c r="P98" s="2">
-        <v>486.0</v>
+        <v>489.0</v>
       </c>
       <c r="Q98" s="2">
         <v>10.0</v>
@@ -7299,7 +7299,7 @@
         <v>14.0</v>
       </c>
       <c r="S98" s="2">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="T98" s="2">
         <v>2.0</v>
@@ -7311,7 +7311,7 @@
         <v>0.0</v>
       </c>
       <c r="W98" s="2">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
@@ -7340,7 +7340,7 @@
         <v>880.0</v>
       </c>
       <c r="I99" s="2">
-        <v>878.0</v>
+        <v>880.0</v>
       </c>
       <c r="J99" s="2">
         <v>798.0</v>
@@ -7414,7 +7414,7 @@
         <v>1254.0</v>
       </c>
       <c r="J100" s="2">
-        <v>1236.0</v>
+        <v>1238.0</v>
       </c>
       <c r="K100" s="2">
         <v>1.0</v>
@@ -7426,13 +7426,13 @@
         <v>0.0</v>
       </c>
       <c r="N100" s="2">
-        <v>1236.0</v>
+        <v>1238.0</v>
       </c>
       <c r="O100" s="2">
-        <v>601.0</v>
+        <v>602.0</v>
       </c>
       <c r="P100" s="2">
-        <v>633.0</v>
+        <v>634.0</v>
       </c>
       <c r="Q100" s="2">
         <v>2.0</v>
@@ -7627,7 +7627,7 @@
         <v>663.0</v>
       </c>
       <c r="J103" s="2">
-        <v>584.0</v>
+        <v>589.0</v>
       </c>
       <c r="K103" s="2">
         <v>1.0</v>
@@ -7639,13 +7639,13 @@
         <v>0.0</v>
       </c>
       <c r="N103" s="2">
-        <v>584.0</v>
+        <v>589.0</v>
       </c>
       <c r="O103" s="2">
-        <v>340.0</v>
+        <v>344.0</v>
       </c>
       <c r="P103" s="2">
-        <v>242.0</v>
+        <v>243.0</v>
       </c>
       <c r="Q103" s="2">
         <v>2.0</v>
@@ -7654,7 +7654,7 @@
         <v>24.0</v>
       </c>
       <c r="S103" s="2">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="T103" s="2">
         <v>0.0</v>
@@ -7666,7 +7666,7 @@
         <v>0.0</v>
       </c>
       <c r="W103" s="2">
-        <v>44.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
@@ -8124,7 +8124,7 @@
         <v>754.0</v>
       </c>
       <c r="J110" s="2">
-        <v>579.0</v>
+        <v>585.0</v>
       </c>
       <c r="K110" s="2">
         <v>1.0</v>
@@ -8136,22 +8136,22 @@
         <v>0.0</v>
       </c>
       <c r="N110" s="2">
-        <v>579.0</v>
+        <v>585.0</v>
       </c>
       <c r="O110" s="2">
         <v>296.0</v>
       </c>
       <c r="P110" s="2">
-        <v>283.0</v>
+        <v>287.0</v>
       </c>
       <c r="Q110" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="R110" s="2">
-        <v>43.0</v>
+        <v>47.0</v>
       </c>
       <c r="S110" s="2">
-        <v>34.0</v>
+        <v>39.0</v>
       </c>
       <c r="T110" s="2">
         <v>1.0</v>
@@ -8163,7 +8163,7 @@
         <v>0.0</v>
       </c>
       <c r="W110" s="2">
-        <v>78.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
@@ -8195,7 +8195,7 @@
         <v>1027.0</v>
       </c>
       <c r="J111" s="2">
-        <v>992.0</v>
+        <v>993.0</v>
       </c>
       <c r="K111" s="2">
         <v>1.0</v>
@@ -8207,10 +8207,10 @@
         <v>0.0</v>
       </c>
       <c r="N111" s="2">
-        <v>992.0</v>
+        <v>993.0</v>
       </c>
       <c r="O111" s="2">
-        <v>556.0</v>
+        <v>557.0</v>
       </c>
       <c r="P111" s="2">
         <v>431.0</v>
@@ -8266,7 +8266,7 @@
         <v>709.0</v>
       </c>
       <c r="J112" s="2">
-        <v>605.0</v>
+        <v>607.0</v>
       </c>
       <c r="K112" s="2">
         <v>1.0</v>
@@ -8278,10 +8278,10 @@
         <v>0.0</v>
       </c>
       <c r="N112" s="2">
-        <v>605.0</v>
+        <v>607.0</v>
       </c>
       <c r="O112" s="2">
-        <v>305.0</v>
+        <v>307.0</v>
       </c>
       <c r="P112" s="2">
         <v>293.0</v>
@@ -8296,7 +8296,7 @@
         <v>56.0</v>
       </c>
       <c r="T112" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="U112" s="2">
         <v>7.0</v>
@@ -8305,7 +8305,7 @@
         <v>0.0</v>
       </c>
       <c r="W112" s="2">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
@@ -8408,7 +8408,7 @@
         <v>924.0</v>
       </c>
       <c r="J114" s="2">
-        <v>669.0</v>
+        <v>675.0</v>
       </c>
       <c r="K114" s="2">
         <v>1.0</v>
@@ -8420,10 +8420,10 @@
         <v>0.0</v>
       </c>
       <c r="N114" s="2">
-        <v>669.0</v>
+        <v>675.0</v>
       </c>
       <c r="O114" s="2">
-        <v>381.0</v>
+        <v>387.0</v>
       </c>
       <c r="P114" s="2">
         <v>287.0</v>
@@ -8432,7 +8432,7 @@
         <v>1.0</v>
       </c>
       <c r="R114" s="2">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="S114" s="2">
         <v>0.0</v>
@@ -8447,7 +8447,7 @@
         <v>0.0</v>
       </c>
       <c r="W114" s="2">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
@@ -8621,7 +8621,7 @@
         <v>1078.0</v>
       </c>
       <c r="J117" s="2">
-        <v>723.0</v>
+        <v>729.0</v>
       </c>
       <c r="K117" s="2">
         <v>1.0</v>
@@ -8633,13 +8633,13 @@
         <v>1.0</v>
       </c>
       <c r="N117" s="2">
-        <v>722.0</v>
+        <v>728.0</v>
       </c>
       <c r="O117" s="2">
-        <v>351.0</v>
+        <v>356.0</v>
       </c>
       <c r="P117" s="2">
-        <v>372.0</v>
+        <v>373.0</v>
       </c>
       <c r="Q117" s="2">
         <v>0.0</v>
@@ -8692,7 +8692,7 @@
         <v>1422.0</v>
       </c>
       <c r="J118" s="2">
-        <v>766.0</v>
+        <v>771.0</v>
       </c>
       <c r="K118" s="2">
         <v>1.0</v>
@@ -8704,13 +8704,13 @@
         <v>0.0</v>
       </c>
       <c r="N118" s="2">
-        <v>766.0</v>
+        <v>771.0</v>
       </c>
       <c r="O118" s="2">
-        <v>408.0</v>
+        <v>410.0</v>
       </c>
       <c r="P118" s="2">
-        <v>354.0</v>
+        <v>357.0</v>
       </c>
       <c r="Q118" s="2">
         <v>4.0</v>
@@ -8834,7 +8834,7 @@
         <v>971.0</v>
       </c>
       <c r="J120" s="2">
-        <v>684.0</v>
+        <v>694.0</v>
       </c>
       <c r="K120" s="2">
         <v>1.0</v>
@@ -8846,13 +8846,13 @@
         <v>0.0</v>
       </c>
       <c r="N120" s="2">
-        <v>684.0</v>
+        <v>694.0</v>
       </c>
       <c r="O120" s="2">
-        <v>365.0</v>
+        <v>373.0</v>
       </c>
       <c r="P120" s="2">
-        <v>316.0</v>
+        <v>318.0</v>
       </c>
       <c r="Q120" s="2">
         <v>3.0</v>
@@ -8905,7 +8905,7 @@
         <v>1425.0</v>
       </c>
       <c r="J121" s="2">
-        <v>769.0</v>
+        <v>779.0</v>
       </c>
       <c r="K121" s="2">
         <v>1.0</v>
@@ -8917,13 +8917,13 @@
         <v>0.0</v>
       </c>
       <c r="N121" s="2">
-        <v>769.0</v>
+        <v>779.0</v>
       </c>
       <c r="O121" s="2">
-        <v>494.0</v>
+        <v>500.0</v>
       </c>
       <c r="P121" s="2">
-        <v>275.0</v>
+        <v>279.0</v>
       </c>
       <c r="Q121" s="2">
         <v>0.0</v>
@@ -9260,7 +9260,7 @@
         <v>1151.0</v>
       </c>
       <c r="J126" s="2">
-        <v>940.0</v>
+        <v>950.0</v>
       </c>
       <c r="K126" s="2">
         <v>1.0</v>
@@ -9272,22 +9272,22 @@
         <v>0.0</v>
       </c>
       <c r="N126" s="2">
-        <v>940.0</v>
+        <v>950.0</v>
       </c>
       <c r="O126" s="2">
-        <v>489.0</v>
+        <v>494.0</v>
       </c>
       <c r="P126" s="2">
-        <v>421.0</v>
+        <v>425.0</v>
       </c>
       <c r="Q126" s="2">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="R126" s="2">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="S126" s="2">
-        <v>28.0</v>
+        <v>33.0</v>
       </c>
       <c r="T126" s="2">
         <v>1.0</v>
@@ -9296,10 +9296,10 @@
         <v>0.0</v>
       </c>
       <c r="V126" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W126" s="2">
-        <v>47.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
@@ -9331,7 +9331,7 @@
         <v>1150.0</v>
       </c>
       <c r="J127" s="2">
-        <v>950.0</v>
+        <v>974.0</v>
       </c>
       <c r="K127" s="2">
         <v>1.0</v>
@@ -9343,34 +9343,34 @@
         <v>0.0</v>
       </c>
       <c r="N127" s="2">
-        <v>950.0</v>
+        <v>974.0</v>
       </c>
       <c r="O127" s="2">
-        <v>600.0</v>
+        <v>616.0</v>
       </c>
       <c r="P127" s="2">
-        <v>350.0</v>
+        <v>358.0</v>
       </c>
       <c r="Q127" s="2">
         <v>0.0</v>
       </c>
       <c r="R127" s="2">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
       <c r="S127" s="2">
-        <v>41.0</v>
+        <v>43.0</v>
       </c>
       <c r="T127" s="2">
         <v>2.0</v>
       </c>
       <c r="U127" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="V127" s="2">
         <v>0.0</v>
       </c>
       <c r="W127" s="2">
-        <v>85.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
@@ -9402,7 +9402,7 @@
         <v>1267.0</v>
       </c>
       <c r="J128" s="2">
-        <v>1094.0</v>
+        <v>1107.0</v>
       </c>
       <c r="K128" s="2">
         <v>1.0</v>
@@ -9414,19 +9414,19 @@
         <v>0.0</v>
       </c>
       <c r="N128" s="2">
-        <v>1094.0</v>
+        <v>1107.0</v>
       </c>
       <c r="O128" s="2">
-        <v>616.0</v>
+        <v>623.0</v>
       </c>
       <c r="P128" s="2">
-        <v>475.0</v>
+        <v>481.0</v>
       </c>
       <c r="Q128" s="2">
         <v>3.0</v>
       </c>
       <c r="R128" s="2">
-        <v>33.0</v>
+        <v>36.0</v>
       </c>
       <c r="S128" s="2">
         <v>15.0</v>
@@ -9435,13 +9435,13 @@
         <v>0.0</v>
       </c>
       <c r="U128" s="2">
-        <v>40.0</v>
+        <v>47.0</v>
       </c>
       <c r="V128" s="2">
         <v>0.0</v>
       </c>
       <c r="W128" s="2">
-        <v>88.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
@@ -9473,7 +9473,7 @@
         <v>1387.0</v>
       </c>
       <c r="J129" s="2">
-        <v>728.0</v>
+        <v>752.0</v>
       </c>
       <c r="K129" s="2">
         <v>1.0</v>
@@ -9485,22 +9485,22 @@
         <v>0.0</v>
       </c>
       <c r="N129" s="2">
-        <v>728.0</v>
+        <v>752.0</v>
       </c>
       <c r="O129" s="2">
-        <v>491.0</v>
+        <v>514.0</v>
       </c>
       <c r="P129" s="2">
-        <v>235.0</v>
+        <v>236.0</v>
       </c>
       <c r="Q129" s="2">
         <v>2.0</v>
       </c>
       <c r="R129" s="2">
-        <v>60.0</v>
+        <v>63.0</v>
       </c>
       <c r="S129" s="2">
-        <v>41.0</v>
+        <v>46.0</v>
       </c>
       <c r="T129" s="2">
         <v>0.0</v>
@@ -9512,7 +9512,7 @@
         <v>0.0</v>
       </c>
       <c r="W129" s="2">
-        <v>101.0</v>
+        <v>109.0</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
@@ -9899,25 +9899,25 @@
         <v>1247.0</v>
       </c>
       <c r="J135" s="2">
+        <v>1069.0</v>
+      </c>
+      <c r="K135" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="L135" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="M135" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="N135" s="2">
         <v>1068.0</v>
-      </c>
-      <c r="K135" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="L135" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="M135" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="N135" s="2">
-        <v>1067.0</v>
       </c>
       <c r="O135" s="2">
         <v>576.0</v>
       </c>
       <c r="P135" s="2">
-        <v>408.0</v>
+        <v>409.0</v>
       </c>
       <c r="Q135" s="2">
         <v>84.0</v>
@@ -9970,7 +9970,7 @@
         <v>1122.0</v>
       </c>
       <c r="J136" s="2">
-        <v>909.0</v>
+        <v>913.0</v>
       </c>
       <c r="K136" s="2">
         <v>1.0</v>
@@ -9982,13 +9982,13 @@
         <v>0.0</v>
       </c>
       <c r="N136" s="2">
-        <v>909.0</v>
+        <v>913.0</v>
       </c>
       <c r="O136" s="2">
-        <v>485.0</v>
+        <v>487.0</v>
       </c>
       <c r="P136" s="2">
-        <v>409.0</v>
+        <v>411.0</v>
       </c>
       <c r="Q136" s="2">
         <v>15.0</v>
@@ -10041,7 +10041,7 @@
         <v>1211.0</v>
       </c>
       <c r="J137" s="2">
-        <v>727.0</v>
+        <v>736.0</v>
       </c>
       <c r="K137" s="2">
         <v>1.0</v>
@@ -10053,10 +10053,10 @@
         <v>0.0</v>
       </c>
       <c r="N137" s="2">
-        <v>727.0</v>
+        <v>736.0</v>
       </c>
       <c r="O137" s="2">
-        <v>371.0</v>
+        <v>380.0</v>
       </c>
       <c r="P137" s="2">
         <v>342.0</v>
@@ -10112,7 +10112,7 @@
         <v>1169.0</v>
       </c>
       <c r="J138" s="2">
-        <v>869.0</v>
+        <v>870.0</v>
       </c>
       <c r="K138" s="2">
         <v>1.0</v>
@@ -10124,10 +10124,10 @@
         <v>0.0</v>
       </c>
       <c r="N138" s="2">
-        <v>869.0</v>
+        <v>870.0</v>
       </c>
       <c r="O138" s="2">
-        <v>520.0</v>
+        <v>521.0</v>
       </c>
       <c r="P138" s="2">
         <v>325.0</v>
@@ -10183,7 +10183,7 @@
         <v>1300.0</v>
       </c>
       <c r="J139" s="2">
-        <v>898.0</v>
+        <v>903.0</v>
       </c>
       <c r="K139" s="2">
         <v>1.0</v>
@@ -10195,10 +10195,10 @@
         <v>0.0</v>
       </c>
       <c r="N139" s="2">
-        <v>898.0</v>
+        <v>903.0</v>
       </c>
       <c r="O139" s="2">
-        <v>548.0</v>
+        <v>553.0</v>
       </c>
       <c r="P139" s="2">
         <v>327.0</v>
@@ -10325,7 +10325,7 @@
         <v>1244.0</v>
       </c>
       <c r="J141" s="2">
-        <v>716.0</v>
+        <v>723.0</v>
       </c>
       <c r="K141" s="2">
         <v>1.0</v>
@@ -10337,34 +10337,34 @@
         <v>1.0</v>
       </c>
       <c r="N141" s="2">
-        <v>715.0</v>
+        <v>722.0</v>
       </c>
       <c r="O141" s="2">
-        <v>426.0</v>
+        <v>431.0</v>
       </c>
       <c r="P141" s="2">
-        <v>290.0</v>
+        <v>292.0</v>
       </c>
       <c r="Q141" s="2">
         <v>0.0</v>
       </c>
       <c r="R141" s="2">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="S141" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="T141" s="2">
         <v>0.0</v>
       </c>
       <c r="U141" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="V141" s="2">
         <v>0.0</v>
       </c>
       <c r="W141" s="2">
-        <v>23.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
@@ -10538,7 +10538,7 @@
         <v>1487.0</v>
       </c>
       <c r="J144" s="2">
-        <v>941.0</v>
+        <v>989.0</v>
       </c>
       <c r="K144" s="2">
         <v>1.0</v>
@@ -10550,13 +10550,13 @@
         <v>0.0</v>
       </c>
       <c r="N144" s="2">
-        <v>941.0</v>
+        <v>989.0</v>
       </c>
       <c r="O144" s="2">
-        <v>524.0</v>
+        <v>546.0</v>
       </c>
       <c r="P144" s="2">
-        <v>417.0</v>
+        <v>443.0</v>
       </c>
       <c r="Q144" s="2">
         <v>0.0</v>
@@ -10822,7 +10822,7 @@
         <v>1269.0</v>
       </c>
       <c r="J148" s="2">
-        <v>860.0</v>
+        <v>862.0</v>
       </c>
       <c r="K148" s="2">
         <v>1.0</v>
@@ -10831,13 +10831,13 @@
         <v>1.0</v>
       </c>
       <c r="M148" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="N148" s="2">
         <v>860.0</v>
       </c>
       <c r="O148" s="2">
-        <v>391.0</v>
+        <v>393.0</v>
       </c>
       <c r="P148" s="2">
         <v>469.0</v>
@@ -10964,7 +10964,7 @@
         <v>971.0</v>
       </c>
       <c r="J150" s="2">
-        <v>803.0</v>
+        <v>830.0</v>
       </c>
       <c r="K150" s="2">
         <v>1.0</v>
@@ -10976,13 +10976,13 @@
         <v>0.0</v>
       </c>
       <c r="N150" s="2">
-        <v>803.0</v>
+        <v>830.0</v>
       </c>
       <c r="O150" s="2">
-        <v>452.0</v>
+        <v>478.0</v>
       </c>
       <c r="P150" s="2">
-        <v>351.0</v>
+        <v>352.0</v>
       </c>
       <c r="Q150" s="2">
         <v>0.0</v>
@@ -11177,7 +11177,7 @@
         <v>1018.0</v>
       </c>
       <c r="J153" s="2">
-        <v>804.0</v>
+        <v>817.0</v>
       </c>
       <c r="K153" s="2">
         <v>1.0</v>
@@ -11189,13 +11189,13 @@
         <v>0.0</v>
       </c>
       <c r="N153" s="2">
-        <v>804.0</v>
+        <v>817.0</v>
       </c>
       <c r="O153" s="2">
-        <v>393.0</v>
+        <v>400.0</v>
       </c>
       <c r="P153" s="2">
-        <v>410.0</v>
+        <v>416.0</v>
       </c>
       <c r="Q153" s="2">
         <v>1.0</v>
@@ -11532,7 +11532,7 @@
         <v>1353.0</v>
       </c>
       <c r="J158" s="2">
-        <v>842.0</v>
+        <v>849.0</v>
       </c>
       <c r="K158" s="2">
         <v>1.0</v>
@@ -11544,13 +11544,13 @@
         <v>0.0</v>
       </c>
       <c r="N158" s="2">
-        <v>842.0</v>
+        <v>849.0</v>
       </c>
       <c r="O158" s="2">
-        <v>383.0</v>
+        <v>387.0</v>
       </c>
       <c r="P158" s="2">
-        <v>459.0</v>
+        <v>462.0</v>
       </c>
       <c r="Q158" s="2">
         <v>0.0</v>
@@ -11603,7 +11603,7 @@
         <v>1153.0</v>
       </c>
       <c r="J159" s="2">
-        <v>881.0</v>
+        <v>886.0</v>
       </c>
       <c r="K159" s="2">
         <v>1.0</v>
@@ -11615,13 +11615,13 @@
         <v>1.0</v>
       </c>
       <c r="N159" s="2">
-        <v>880.0</v>
+        <v>885.0</v>
       </c>
       <c r="O159" s="2">
-        <v>511.0</v>
+        <v>514.0</v>
       </c>
       <c r="P159" s="2">
-        <v>370.0</v>
+        <v>372.0</v>
       </c>
       <c r="Q159" s="2">
         <v>0.0</v>
@@ -11816,7 +11816,7 @@
         <v>1184.0</v>
       </c>
       <c r="J162" s="2">
-        <v>852.0</v>
+        <v>855.0</v>
       </c>
       <c r="K162" s="2">
         <v>1.0</v>
@@ -11828,19 +11828,19 @@
         <v>1.0</v>
       </c>
       <c r="N162" s="2">
-        <v>851.0</v>
+        <v>854.0</v>
       </c>
       <c r="O162" s="2">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="P162" s="2">
-        <v>198.0</v>
+        <v>200.0</v>
       </c>
       <c r="Q162" s="2">
         <v>619.0</v>
       </c>
       <c r="R162" s="2">
-        <v>8.0</v>
+        <v>17.0</v>
       </c>
       <c r="S162" s="2">
         <v>0.0</v>
@@ -11855,7 +11855,7 @@
         <v>0.0</v>
       </c>
       <c r="W162" s="2">
-        <v>8.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="163" ht="15.75" customHeight="1">
@@ -11887,7 +11887,7 @@
         <v>1298.0</v>
       </c>
       <c r="J163" s="2">
-        <v>733.0</v>
+        <v>738.0</v>
       </c>
       <c r="K163" s="2">
         <v>1.0</v>
@@ -11899,16 +11899,16 @@
         <v>0.0</v>
       </c>
       <c r="N163" s="2">
-        <v>733.0</v>
+        <v>738.0</v>
       </c>
       <c r="O163" s="2">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="P163" s="2">
-        <v>331.0</v>
+        <v>332.0</v>
       </c>
       <c r="Q163" s="2">
-        <v>380.0</v>
+        <v>381.0</v>
       </c>
       <c r="R163" s="2">
         <v>36.0</v>
@@ -11958,7 +11958,7 @@
         <v>1054.0</v>
       </c>
       <c r="J164" s="2">
-        <v>760.0</v>
+        <v>770.0</v>
       </c>
       <c r="K164" s="2">
         <v>1.0</v>
@@ -11970,16 +11970,16 @@
         <v>1.0</v>
       </c>
       <c r="N164" s="2">
-        <v>759.0</v>
+        <v>769.0</v>
       </c>
       <c r="O164" s="2">
         <v>32.0</v>
       </c>
       <c r="P164" s="2">
-        <v>337.0</v>
+        <v>342.0</v>
       </c>
       <c r="Q164" s="2">
-        <v>391.0</v>
+        <v>396.0</v>
       </c>
       <c r="R164" s="2">
         <v>43.0</v>
@@ -12242,7 +12242,7 @@
         <v>948.0</v>
       </c>
       <c r="J168" s="2">
-        <v>667.0</v>
+        <v>683.0</v>
       </c>
       <c r="K168" s="2">
         <v>1.0</v>
@@ -12254,13 +12254,13 @@
         <v>0.0</v>
       </c>
       <c r="N168" s="2">
-        <v>667.0</v>
+        <v>683.0</v>
       </c>
       <c r="O168" s="2">
-        <v>228.0</v>
+        <v>231.0</v>
       </c>
       <c r="P168" s="2">
-        <v>351.0</v>
+        <v>364.0</v>
       </c>
       <c r="Q168" s="2">
         <v>88.0</v>
@@ -12313,7 +12313,7 @@
         <v>503.0</v>
       </c>
       <c r="J169" s="2">
-        <v>460.0</v>
+        <v>461.0</v>
       </c>
       <c r="K169" s="2">
         <v>1.0</v>
@@ -12325,13 +12325,13 @@
         <v>0.0</v>
       </c>
       <c r="N169" s="2">
-        <v>460.0</v>
+        <v>461.0</v>
       </c>
       <c r="O169" s="2">
-        <v>239.0</v>
+        <v>241.0</v>
       </c>
       <c r="P169" s="2">
-        <v>213.0</v>
+        <v>212.0</v>
       </c>
       <c r="Q169" s="2">
         <v>8.0</v>
@@ -12526,7 +12526,7 @@
         <v>1079.0</v>
       </c>
       <c r="J172" s="2">
-        <v>540.0</v>
+        <v>552.0</v>
       </c>
       <c r="K172" s="2">
         <v>1.0</v>
@@ -12538,13 +12538,13 @@
         <v>0.0</v>
       </c>
       <c r="N172" s="2">
-        <v>540.0</v>
+        <v>552.0</v>
       </c>
       <c r="O172" s="2">
-        <v>285.0</v>
+        <v>293.0</v>
       </c>
       <c r="P172" s="2">
-        <v>255.0</v>
+        <v>259.0</v>
       </c>
       <c r="Q172" s="2">
         <v>0.0</v>
@@ -12810,7 +12810,7 @@
         <v>1045.0</v>
       </c>
       <c r="J176" s="2">
-        <v>619.0</v>
+        <v>621.0</v>
       </c>
       <c r="K176" s="2">
         <v>1.0</v>
@@ -12822,13 +12822,13 @@
         <v>0.0</v>
       </c>
       <c r="N176" s="2">
-        <v>619.0</v>
+        <v>621.0</v>
       </c>
       <c r="O176" s="2">
-        <v>273.0</v>
+        <v>274.0</v>
       </c>
       <c r="P176" s="2">
-        <v>345.0</v>
+        <v>346.0</v>
       </c>
       <c r="Q176" s="2">
         <v>1.0</v>
@@ -12881,7 +12881,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" s="2">
-        <v>565.0</v>
+        <v>570.0</v>
       </c>
       <c r="K177" s="2">
         <v>1.0</v>
@@ -12893,10 +12893,10 @@
         <v>0.0</v>
       </c>
       <c r="N177" s="2">
-        <v>565.0</v>
+        <v>570.0</v>
       </c>
       <c r="O177" s="2">
-        <v>315.0</v>
+        <v>320.0</v>
       </c>
       <c r="P177" s="2">
         <v>250.0</v>
@@ -12952,7 +12952,7 @@
         <v>1008.0</v>
       </c>
       <c r="J178" s="2">
-        <v>507.0</v>
+        <v>526.0</v>
       </c>
       <c r="K178" s="2">
         <v>1.0</v>
@@ -12964,19 +12964,19 @@
         <v>0.0</v>
       </c>
       <c r="N178" s="2">
-        <v>507.0</v>
+        <v>526.0</v>
       </c>
       <c r="O178" s="2">
-        <v>225.0</v>
+        <v>238.0</v>
       </c>
       <c r="P178" s="2">
-        <v>281.0</v>
+        <v>287.0</v>
       </c>
       <c r="Q178" s="2">
         <v>1.0</v>
       </c>
       <c r="R178" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="S178" s="2">
         <v>7.0</v>
@@ -12985,13 +12985,13 @@
         <v>1.0</v>
       </c>
       <c r="U178" s="2">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
       <c r="V178" s="2">
         <v>0.0</v>
       </c>
       <c r="W178" s="2">
-        <v>89.0</v>
+        <v>93.0</v>
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1">
@@ -13023,7 +13023,7 @@
         <v>1061.0</v>
       </c>
       <c r="J179" s="2">
-        <v>720.0</v>
+        <v>725.0</v>
       </c>
       <c r="K179" s="2">
         <v>1.0</v>
@@ -13035,13 +13035,13 @@
         <v>0.0</v>
       </c>
       <c r="N179" s="2">
-        <v>720.0</v>
+        <v>725.0</v>
       </c>
       <c r="O179" s="2">
-        <v>444.0</v>
+        <v>447.0</v>
       </c>
       <c r="P179" s="2">
-        <v>275.0</v>
+        <v>277.0</v>
       </c>
       <c r="Q179" s="2">
         <v>1.0</v>
@@ -13165,7 +13165,7 @@
         <v>855.0</v>
       </c>
       <c r="J181" s="2">
-        <v>467.0</v>
+        <v>473.0</v>
       </c>
       <c r="K181" s="2">
         <v>1.0</v>
@@ -13177,13 +13177,13 @@
         <v>0.0</v>
       </c>
       <c r="N181" s="2">
-        <v>467.0</v>
+        <v>473.0</v>
       </c>
       <c r="O181" s="2">
-        <v>246.0</v>
+        <v>247.0</v>
       </c>
       <c r="P181" s="2">
-        <v>221.0</v>
+        <v>226.0</v>
       </c>
       <c r="Q181" s="2">
         <v>0.0</v>
@@ -13520,7 +13520,7 @@
         <v>1067.0</v>
       </c>
       <c r="J186" s="2">
-        <v>832.0</v>
+        <v>845.0</v>
       </c>
       <c r="K186" s="2">
         <v>1.0</v>
@@ -13532,13 +13532,13 @@
         <v>0.0</v>
       </c>
       <c r="N186" s="2">
-        <v>832.0</v>
+        <v>845.0</v>
       </c>
       <c r="O186" s="2">
-        <v>231.0</v>
+        <v>238.0</v>
       </c>
       <c r="P186" s="2">
-        <v>346.0</v>
+        <v>352.0</v>
       </c>
       <c r="Q186" s="2">
         <v>255.0</v>
@@ -13547,7 +13547,7 @@
         <v>15.0</v>
       </c>
       <c r="S186" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="T186" s="2">
         <v>0.0</v>
@@ -13559,7 +13559,7 @@
         <v>0.0</v>
       </c>
       <c r="W186" s="2">
-        <v>16.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="187" ht="15.75" customHeight="1">
@@ -13662,7 +13662,7 @@
         <v>1017.0</v>
       </c>
       <c r="J188" s="2">
-        <v>874.0</v>
+        <v>875.0</v>
       </c>
       <c r="K188" s="2">
         <v>1.0</v>
@@ -13674,10 +13674,10 @@
         <v>0.0</v>
       </c>
       <c r="N188" s="2">
-        <v>874.0</v>
+        <v>875.0</v>
       </c>
       <c r="O188" s="2">
-        <v>429.0</v>
+        <v>430.0</v>
       </c>
       <c r="P188" s="2">
         <v>387.0</v>
@@ -13875,7 +13875,7 @@
         <v>1363.0</v>
       </c>
       <c r="J191" s="2">
-        <v>917.0</v>
+        <v>918.0</v>
       </c>
       <c r="K191" s="2">
         <v>1.0</v>
@@ -13887,13 +13887,13 @@
         <v>0.0</v>
       </c>
       <c r="N191" s="2">
-        <v>917.0</v>
+        <v>918.0</v>
       </c>
       <c r="O191" s="2">
         <v>504.0</v>
       </c>
       <c r="P191" s="2">
-        <v>380.0</v>
+        <v>381.0</v>
       </c>
       <c r="Q191" s="2">
         <v>33.0</v>
@@ -13946,7 +13946,7 @@
         <v>508.0</v>
       </c>
       <c r="J192" s="2">
-        <v>439.0</v>
+        <v>455.0</v>
       </c>
       <c r="K192" s="2">
         <v>1.0</v>
@@ -13958,25 +13958,25 @@
         <v>0.0</v>
       </c>
       <c r="N192" s="2">
-        <v>439.0</v>
+        <v>455.0</v>
       </c>
       <c r="O192" s="2">
-        <v>275.0</v>
+        <v>285.0</v>
       </c>
       <c r="P192" s="2">
-        <v>161.0</v>
+        <v>167.0</v>
       </c>
       <c r="Q192" s="2">
         <v>3.0</v>
       </c>
       <c r="R192" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="S192" s="2">
         <v>5.0</v>
       </c>
       <c r="T192" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="U192" s="2">
         <v>0.0</v>
@@ -13985,7 +13985,7 @@
         <v>0.0</v>
       </c>
       <c r="W192" s="2">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1">
@@ -14017,7 +14017,7 @@
         <v>1326.0</v>
       </c>
       <c r="J193" s="2">
-        <v>1081.0</v>
+        <v>1118.0</v>
       </c>
       <c r="K193" s="2">
         <v>1.0</v>
@@ -14029,16 +14029,16 @@
         <v>0.0</v>
       </c>
       <c r="N193" s="2">
-        <v>1081.0</v>
+        <v>1118.0</v>
       </c>
       <c r="O193" s="2">
-        <v>391.0</v>
+        <v>414.0</v>
       </c>
       <c r="P193" s="2">
-        <v>476.0</v>
+        <v>489.0</v>
       </c>
       <c r="Q193" s="2">
-        <v>214.0</v>
+        <v>215.0</v>
       </c>
       <c r="R193" s="2">
         <v>19.0</v>
@@ -14159,7 +14159,7 @@
         <v>556.0</v>
       </c>
       <c r="J195" s="2">
-        <v>426.0</v>
+        <v>440.0</v>
       </c>
       <c r="K195" s="2">
         <v>1.0</v>
@@ -14171,13 +14171,13 @@
         <v>0.0</v>
       </c>
       <c r="N195" s="2">
-        <v>426.0</v>
+        <v>440.0</v>
       </c>
       <c r="O195" s="2">
-        <v>135.0</v>
+        <v>147.0</v>
       </c>
       <c r="P195" s="2">
-        <v>165.0</v>
+        <v>167.0</v>
       </c>
       <c r="Q195" s="2">
         <v>126.0</v>
@@ -14372,7 +14372,7 @@
         <v>1477.0</v>
       </c>
       <c r="J198" s="2">
-        <v>1199.0</v>
+        <v>1204.0</v>
       </c>
       <c r="K198" s="2">
         <v>1.0</v>
@@ -14384,13 +14384,13 @@
         <v>0.0</v>
       </c>
       <c r="N198" s="2">
-        <v>1199.0</v>
+        <v>1204.0</v>
       </c>
       <c r="O198" s="2">
-        <v>335.0</v>
+        <v>337.0</v>
       </c>
       <c r="P198" s="2">
-        <v>589.0</v>
+        <v>592.0</v>
       </c>
       <c r="Q198" s="2">
         <v>275.0</v>
@@ -14443,7 +14443,7 @@
         <v>1015.0</v>
       </c>
       <c r="J199" s="2">
-        <v>902.0</v>
+        <v>903.0</v>
       </c>
       <c r="K199" s="2">
         <v>1.0</v>
@@ -14455,13 +14455,13 @@
         <v>0.0</v>
       </c>
       <c r="N199" s="2">
-        <v>902.0</v>
+        <v>903.0</v>
       </c>
       <c r="O199" s="2">
         <v>442.0</v>
       </c>
       <c r="P199" s="2">
-        <v>460.0</v>
+        <v>461.0</v>
       </c>
       <c r="Q199" s="2">
         <v>0.0</v>
@@ -14514,7 +14514,7 @@
         <v>704.0</v>
       </c>
       <c r="J200" s="2">
-        <v>546.0</v>
+        <v>564.0</v>
       </c>
       <c r="K200" s="2">
         <v>1.0</v>
@@ -14526,19 +14526,19 @@
         <v>0.0</v>
       </c>
       <c r="N200" s="2">
-        <v>546.0</v>
+        <v>564.0</v>
       </c>
       <c r="O200" s="2">
-        <v>323.0</v>
+        <v>332.0</v>
       </c>
       <c r="P200" s="2">
-        <v>220.0</v>
+        <v>229.0</v>
       </c>
       <c r="Q200" s="2">
         <v>3.0</v>
       </c>
       <c r="R200" s="2">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="S200" s="2">
         <v>39.0</v>
@@ -14553,7 +14553,7 @@
         <v>3.0</v>
       </c>
       <c r="W200" s="2">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="201" ht="15.75" customHeight="1">
@@ -14656,7 +14656,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" s="2">
-        <v>741.0</v>
+        <v>770.0</v>
       </c>
       <c r="K202" s="2">
         <v>1.0</v>
@@ -14668,13 +14668,13 @@
         <v>0.0</v>
       </c>
       <c r="N202" s="2">
-        <v>741.0</v>
+        <v>770.0</v>
       </c>
       <c r="O202" s="2">
-        <v>434.0</v>
+        <v>455.0</v>
       </c>
       <c r="P202" s="2">
-        <v>307.0</v>
+        <v>315.0</v>
       </c>
       <c r="Q202" s="2">
         <v>0.0</v>
@@ -14751,14 +14751,14 @@
         <v>1.0</v>
       </c>
       <c r="R203" s="2">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="S203" s="2">
+        <v>23.0</v>
+      </c>
+      <c r="T203" s="2">
         <v>5.0</v>
       </c>
-      <c r="T203" s="2">
-        <v>4.0</v>
-      </c>
       <c r="U203" s="2">
         <v>0.0</v>
       </c>
@@ -14766,7 +14766,7 @@
         <v>0.0</v>
       </c>
       <c r="W203" s="2">
-        <v>62.0</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="204" ht="15.75" customHeight="1">
@@ -14869,7 +14869,7 @@
         <v>897.0</v>
       </c>
       <c r="J205" s="2">
-        <v>624.0</v>
+        <v>641.0</v>
       </c>
       <c r="K205" s="2">
         <v>1.0</v>
@@ -14881,16 +14881,16 @@
         <v>0.0</v>
       </c>
       <c r="N205" s="2">
-        <v>624.0</v>
+        <v>641.0</v>
       </c>
       <c r="O205" s="2">
-        <v>323.0</v>
+        <v>332.0</v>
       </c>
       <c r="P205" s="2">
-        <v>261.0</v>
+        <v>268.0</v>
       </c>
       <c r="Q205" s="2">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="R205" s="2">
         <v>5.0</v>
@@ -14940,7 +14940,7 @@
         <v>859.0</v>
       </c>
       <c r="J206" s="2">
-        <v>731.0</v>
+        <v>743.0</v>
       </c>
       <c r="K206" s="2">
         <v>1.0</v>
@@ -14952,13 +14952,13 @@
         <v>0.0</v>
       </c>
       <c r="N206" s="2">
-        <v>731.0</v>
+        <v>743.0</v>
       </c>
       <c r="O206" s="2">
-        <v>456.0</v>
+        <v>467.0</v>
       </c>
       <c r="P206" s="2">
-        <v>275.0</v>
+        <v>276.0</v>
       </c>
       <c r="Q206" s="2">
         <v>0.0</v>
@@ -15011,7 +15011,7 @@
         <v>943.0</v>
       </c>
       <c r="J207" s="2">
-        <v>576.0</v>
+        <v>593.0</v>
       </c>
       <c r="K207" s="2">
         <v>1.0</v>
@@ -15023,23 +15023,23 @@
         <v>0.0</v>
       </c>
       <c r="N207" s="2">
-        <v>576.0</v>
+        <v>593.0</v>
       </c>
       <c r="O207" s="2">
-        <v>327.0</v>
+        <v>332.0</v>
       </c>
       <c r="P207" s="2">
-        <v>242.0</v>
+        <v>251.0</v>
       </c>
       <c r="Q207" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="R207" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="S207" s="2">
         <v>7.0</v>
       </c>
-      <c r="R207" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="S207" s="2">
-        <v>6.0</v>
-      </c>
       <c r="T207" s="2">
         <v>0.0</v>
       </c>
@@ -15050,7 +15050,7 @@
         <v>0.0</v>
       </c>
       <c r="W207" s="2">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="208" ht="15.75" customHeight="1">
@@ -15153,7 +15153,7 @@
         <v>951.0</v>
       </c>
       <c r="J209" s="2">
-        <v>839.0</v>
+        <v>840.0</v>
       </c>
       <c r="K209" s="2">
         <v>1.0</v>
@@ -15165,13 +15165,13 @@
         <v>0.0</v>
       </c>
       <c r="N209" s="2">
-        <v>839.0</v>
+        <v>840.0</v>
       </c>
       <c r="O209" s="2">
         <v>436.0</v>
       </c>
       <c r="P209" s="2">
-        <v>403.0</v>
+        <v>404.0</v>
       </c>
       <c r="Q209" s="2">
         <v>0.0</v>
@@ -15180,7 +15180,7 @@
         <v>47.0</v>
       </c>
       <c r="S209" s="2">
-        <v>16.0</v>
+        <v>27.0</v>
       </c>
       <c r="T209" s="2">
         <v>6.0</v>
@@ -15189,10 +15189,10 @@
         <v>0.0</v>
       </c>
       <c r="V209" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W209" s="2">
-        <v>69.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="210" ht="15.75" customHeight="1">
@@ -15295,7 +15295,7 @@
         <v>1074.0</v>
       </c>
       <c r="J211" s="2">
-        <v>850.0</v>
+        <v>863.0</v>
       </c>
       <c r="K211" s="2">
         <v>1.0</v>
@@ -15307,13 +15307,13 @@
         <v>0.0</v>
       </c>
       <c r="N211" s="2">
-        <v>850.0</v>
+        <v>863.0</v>
       </c>
       <c r="O211" s="2">
-        <v>438.0</v>
+        <v>446.0</v>
       </c>
       <c r="P211" s="2">
-        <v>412.0</v>
+        <v>417.0</v>
       </c>
       <c r="Q211" s="2">
         <v>0.0</v>
@@ -15366,7 +15366,7 @@
         <v>1055.0</v>
       </c>
       <c r="J212" s="2">
-        <v>789.0</v>
+        <v>802.0</v>
       </c>
       <c r="K212" s="2">
         <v>1.0</v>
@@ -15378,13 +15378,13 @@
         <v>1.0</v>
       </c>
       <c r="N212" s="2">
-        <v>788.0</v>
+        <v>801.0</v>
       </c>
       <c r="O212" s="2">
-        <v>202.0</v>
+        <v>210.0</v>
       </c>
       <c r="P212" s="2">
-        <v>367.0</v>
+        <v>372.0</v>
       </c>
       <c r="Q212" s="2">
         <v>220.0</v>
@@ -15437,7 +15437,7 @@
         <v>1034.0</v>
       </c>
       <c r="J213" s="2">
-        <v>770.0</v>
+        <v>776.0</v>
       </c>
       <c r="K213" s="2">
         <v>1.0</v>
@@ -15449,13 +15449,13 @@
         <v>0.0</v>
       </c>
       <c r="N213" s="2">
-        <v>770.0</v>
+        <v>776.0</v>
       </c>
       <c r="O213" s="2">
-        <v>440.0</v>
+        <v>443.0</v>
       </c>
       <c r="P213" s="2">
-        <v>330.0</v>
+        <v>333.0</v>
       </c>
       <c r="Q213" s="2">
         <v>0.0</v>
@@ -15579,7 +15579,7 @@
         <v>1067.0</v>
       </c>
       <c r="J215" s="2">
-        <v>940.0</v>
+        <v>953.0</v>
       </c>
       <c r="K215" s="2">
         <v>1.0</v>
@@ -15591,13 +15591,13 @@
         <v>0.0</v>
       </c>
       <c r="N215" s="2">
-        <v>940.0</v>
+        <v>953.0</v>
       </c>
       <c r="O215" s="2">
-        <v>477.0</v>
+        <v>483.0</v>
       </c>
       <c r="P215" s="2">
-        <v>454.0</v>
+        <v>461.0</v>
       </c>
       <c r="Q215" s="2">
         <v>9.0</v>
@@ -15612,13 +15612,13 @@
         <v>6.0</v>
       </c>
       <c r="U215" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="V215" s="2">
         <v>0.0</v>
       </c>
       <c r="W215" s="2">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="216" ht="15.75" customHeight="1">
@@ -15721,7 +15721,7 @@
         <v>1136.0</v>
       </c>
       <c r="J217" s="2">
-        <v>710.0</v>
+        <v>714.0</v>
       </c>
       <c r="K217" s="2">
         <v>1.0</v>
@@ -15733,13 +15733,13 @@
         <v>0.0</v>
       </c>
       <c r="N217" s="2">
-        <v>710.0</v>
+        <v>714.0</v>
       </c>
       <c r="O217" s="2">
         <v>344.0</v>
       </c>
       <c r="P217" s="2">
-        <v>366.0</v>
+        <v>370.0</v>
       </c>
       <c r="Q217" s="2">
         <v>0.0</v>
@@ -15792,7 +15792,7 @@
         <v>1197.0</v>
       </c>
       <c r="J218" s="2">
-        <v>694.0</v>
+        <v>699.0</v>
       </c>
       <c r="K218" s="2">
         <v>1.0</v>
@@ -15804,34 +15804,34 @@
         <v>1.0</v>
       </c>
       <c r="N218" s="2">
-        <v>693.0</v>
+        <v>698.0</v>
       </c>
       <c r="O218" s="2">
-        <v>355.0</v>
+        <v>356.0</v>
       </c>
       <c r="P218" s="2">
-        <v>339.0</v>
+        <v>343.0</v>
       </c>
       <c r="Q218" s="2">
         <v>0.0</v>
       </c>
       <c r="R218" s="2">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="S218" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="T218" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="U218" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V218" s="2">
         <v>0.0</v>
       </c>
       <c r="W218" s="2">
-        <v>43.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="219" ht="15.75" customHeight="1">
@@ -15863,7 +15863,7 @@
         <v>1433.0</v>
       </c>
       <c r="J219" s="2">
-        <v>952.0</v>
+        <v>957.0</v>
       </c>
       <c r="K219" s="2">
         <v>1.0</v>
@@ -15875,16 +15875,16 @@
         <v>0.0</v>
       </c>
       <c r="N219" s="2">
-        <v>952.0</v>
+        <v>957.0</v>
       </c>
       <c r="O219" s="2">
-        <v>167.0</v>
+        <v>169.0</v>
       </c>
       <c r="P219" s="2">
         <v>410.0</v>
       </c>
       <c r="Q219" s="2">
-        <v>375.0</v>
+        <v>378.0</v>
       </c>
       <c r="R219" s="2">
         <v>24.0</v>
@@ -16005,7 +16005,7 @@
         <v>848.0</v>
       </c>
       <c r="J221" s="2">
-        <v>693.0</v>
+        <v>728.0</v>
       </c>
       <c r="K221" s="2">
         <v>1.0</v>
@@ -16017,16 +16017,16 @@
         <v>1.0</v>
       </c>
       <c r="N221" s="2">
-        <v>692.0</v>
+        <v>727.0</v>
       </c>
       <c r="O221" s="2">
-        <v>171.0</v>
+        <v>204.0</v>
       </c>
       <c r="P221" s="2">
-        <v>276.0</v>
+        <v>277.0</v>
       </c>
       <c r="Q221" s="2">
-        <v>246.0</v>
+        <v>247.0</v>
       </c>
       <c r="R221" s="2">
         <v>2.0</v>
@@ -16076,7 +16076,7 @@
         <v>1043.0</v>
       </c>
       <c r="J222" s="2">
-        <v>721.0</v>
+        <v>724.0</v>
       </c>
       <c r="K222" s="2">
         <v>1.0</v>
@@ -16088,13 +16088,13 @@
         <v>0.0</v>
       </c>
       <c r="N222" s="2">
-        <v>721.0</v>
+        <v>724.0</v>
       </c>
       <c r="O222" s="2">
-        <v>178.0</v>
+        <v>179.0</v>
       </c>
       <c r="P222" s="2">
-        <v>307.0</v>
+        <v>309.0</v>
       </c>
       <c r="Q222" s="2">
         <v>236.0</v>
@@ -16171,10 +16171,10 @@
         <v>474.0</v>
       </c>
       <c r="R223" s="2">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="S223" s="2">
-        <v>0.0</v>
+        <v>31.0</v>
       </c>
       <c r="T223" s="2">
         <v>0.0</v>
@@ -16186,7 +16186,7 @@
         <v>0.0</v>
       </c>
       <c r="W223" s="2">
-        <v>70.0</v>
+        <v>102.0</v>
       </c>
     </row>
     <row r="224" ht="15.75" customHeight="1">
@@ -16218,7 +16218,7 @@
         <v>766.0</v>
       </c>
       <c r="J224" s="2">
-        <v>575.0</v>
+        <v>581.0</v>
       </c>
       <c r="K224" s="2">
         <v>1.0</v>
@@ -16230,7 +16230,7 @@
         <v>0.0</v>
       </c>
       <c r="N224" s="2">
-        <v>575.0</v>
+        <v>581.0</v>
       </c>
       <c r="O224" s="2">
         <v>22.0</v>
@@ -16239,7 +16239,7 @@
         <v>38.0</v>
       </c>
       <c r="Q224" s="2">
-        <v>515.0</v>
+        <v>521.0</v>
       </c>
       <c r="R224" s="2">
         <v>2.0</v>
@@ -16502,7 +16502,7 @@
         <v>1402.0</v>
       </c>
       <c r="J228" s="2">
-        <v>906.0</v>
+        <v>907.0</v>
       </c>
       <c r="K228" s="2">
         <v>1.0</v>
@@ -16514,7 +16514,7 @@
         <v>0.0</v>
       </c>
       <c r="N228" s="2">
-        <v>906.0</v>
+        <v>907.0</v>
       </c>
       <c r="O228" s="2">
         <v>223.0</v>
@@ -16523,13 +16523,13 @@
         <v>355.0</v>
       </c>
       <c r="Q228" s="2">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="R228" s="2">
-        <v>19.0</v>
+        <v>23.0</v>
       </c>
       <c r="S228" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="T228" s="2">
         <v>0.0</v>
@@ -16541,7 +16541,7 @@
         <v>0.0</v>
       </c>
       <c r="W228" s="2">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="229" ht="15.75" customHeight="1">
@@ -16857,7 +16857,7 @@
         <v>666.0</v>
       </c>
       <c r="J233" s="2">
-        <v>524.0</v>
+        <v>536.0</v>
       </c>
       <c r="K233" s="2">
         <v>1.0</v>
@@ -16869,16 +16869,16 @@
         <v>0.0</v>
       </c>
       <c r="N233" s="2">
-        <v>524.0</v>
+        <v>536.0</v>
       </c>
       <c r="O233" s="2">
-        <v>126.0</v>
+        <v>137.0</v>
       </c>
       <c r="P233" s="2">
         <v>254.0</v>
       </c>
       <c r="Q233" s="2">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="R233" s="2">
         <v>7.0</v>
